--- a/data/trans_orig/P32D_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P32D_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 12 meses ha tomado 6/5 (Hombre/Mujer) o más bebidas estándar en una misma ocasión en 2023</t>
+          <t>Población según si en los últimos 12 meses ha tomado 6/5 (Hombre/Mujer) o más bebidas estándar en una misma ocasión en 2023 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40296</t>
+          <t>41014</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62317</t>
+          <t>63976</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28383</t>
+          <t>28130</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41039</t>
+          <t>41209</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71475</t>
+          <t>73411</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>99358</t>
+          <t>101752</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>33,23%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83207</t>
+          <t>83383</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>110366</t>
+          <t>110141</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14228</t>
+          <t>13807</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25220</t>
+          <t>24669</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101380</t>
+          <t>101160</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>130328</t>
+          <t>131514</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,95%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38683</t>
+          <t>40347</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>63350</t>
+          <t>63818</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10284</t>
+          <t>10459</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44921</t>
+          <t>43924</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>70721</t>
+          <t>68560</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9097</t>
+          <t>8826</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23613</t>
+          <t>22725</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>744</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5497</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10443</t>
+          <t>10667</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25694</t>
+          <t>25128</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4378</t>
+          <t>4299</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15582</t>
+          <t>15133</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>491</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5583</t>
+          <t>5614</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17970</t>
+          <t>17729</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15472</t>
+          <t>15710</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>368</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>4229</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16380</t>
+          <t>17006</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7947</t>
+          <t>8182</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8451</t>
+          <t>8574</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6339</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1556,62 +1556,62 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1037</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>6329</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>7226</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10376</t>
+          <t>11143</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6049</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13311</t>
+          <t>12582</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>175476</t>
+          <t>173956</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>245194</t>
+          <t>246405</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>280418</t>
+          <t>277942</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>583123</t>
+          <t>575148</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>455946</t>
+          <t>454868</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1010643</t>
+          <t>998842</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,06%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>366640</t>
+          <t>367998</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>437646</t>
+          <t>438116</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>67836</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>250264</t>
+          <t>248229</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>374220</t>
+          <t>373098</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>674764</t>
+          <t>669744</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,6%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>176009</t>
+          <t>176755</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>237235</t>
+          <t>234585</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33615</t>
+          <t>36024</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>124447</t>
+          <t>126502</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>185623</t>
+          <t>193089</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>341999</t>
+          <t>339878</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -2203,12 +2203,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55965</t>
+          <t>54585</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95482</t>
+          <t>94700</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7391</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34200</t>
+          <t>33898</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>61200</t>
+          <t>62025</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>121234</t>
+          <t>124156</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -2316,12 +2316,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31518</t>
+          <t>31025</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62206</t>
+          <t>61661</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4364</t>
+          <t>4108</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21879</t>
+          <t>22259</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>37135</t>
+          <t>34585</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>78897</t>
+          <t>75345</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -2429,12 +2429,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20185</t>
+          <t>20522</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45785</t>
+          <t>46497</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13168</t>
+          <t>14027</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22893</t>
+          <t>23002</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55563</t>
+          <t>53908</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4942</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2577,12 +2577,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>329</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6730</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>8609</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2655,12 +2655,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>878</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>10598</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>841</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>10565</t>
+          <t>10912</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6381</t>
+          <t>6085</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19804</t>
+          <t>19994</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>5537</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6982</t>
+          <t>6896</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22447</t>
+          <t>22493</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>66478</t>
+          <t>67727</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>102176</t>
+          <t>103812</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>86887</t>
+          <t>89002</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>114940</t>
+          <t>115688</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3068,12 +3068,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>164166</t>
+          <t>164098</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>209771</t>
+          <t>210464</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,86%</t>
         </is>
       </c>
     </row>
@@ -3111,12 +3111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>117476</t>
+          <t>114519</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>157828</t>
+          <t>152750</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3126,12 +3126,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>58152</t>
+          <t>57968</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>82157</t>
+          <t>83919</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>182886</t>
+          <t>181804</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>229804</t>
+          <t>230003</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,19%</t>
         </is>
       </c>
     </row>
@@ -3224,12 +3224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>52371</t>
+          <t>54592</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>87447</t>
+          <t>87603</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>31293</t>
+          <t>30127</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>52385</t>
+          <t>52493</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>90671</t>
+          <t>91379</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>131663</t>
+          <t>131589</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,42%</t>
         </is>
       </c>
     </row>
@@ -3337,12 +3337,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>16184</t>
+          <t>16538</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>63926</t>
+          <t>59014</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2656</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>12042</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>22797</t>
+          <t>21658</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>65496</t>
+          <t>67896</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -3450,12 +3450,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17391</t>
+          <t>18986</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3465,12 +3465,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>20752</t>
+          <t>21030</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11926</t>
+          <t>12503</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>32202</t>
+          <t>32019</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -3563,12 +3563,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7246</t>
+          <t>7492</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>21062</t>
+          <t>22400</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3598,12 +3598,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5822</t>
+          <t>6185</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>22571</t>
+          <t>23055</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>16368</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>37531</t>
+          <t>38089</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6928</t>
+          <t>6194</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3730</t>
+          <t>3625</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3824,62 +3824,62 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>1313</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>3999</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>722</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>3739</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>402</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4691</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>913</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -4132,12 +4132,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>304485</t>
+          <t>301778</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>385969</t>
+          <t>385532</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>415480</t>
+          <t>415852</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>768388</t>
+          <t>757285</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>722282</t>
+          <t>729018</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1313457</t>
+          <t>1309817</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>50,68%</t>
         </is>
       </c>
     </row>
@@ -4245,12 +4245,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>595985</t>
+          <t>591320</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>683034</t>
+          <t>683937</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4280,12 +4280,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>131943</t>
+          <t>145044</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>337302</t>
+          <t>335874</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4295,12 +4295,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4315,12 +4315,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>684087</t>
+          <t>692774</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>991392</t>
+          <t>996622</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,56%</t>
         </is>
       </c>
     </row>
@@ -4358,12 +4358,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>285482</t>
+          <t>287721</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>358785</t>
+          <t>362787</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4373,12 +4373,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>60473</t>
+          <t>70917</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>171418</t>
+          <t>173051</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>348589</t>
+          <t>332923</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>509166</t>
+          <t>507483</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -4471,12 +4471,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>93776</t>
+          <t>94506</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>150233</t>
+          <t>151648</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4486,12 +4486,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>15408</t>
+          <t>14003</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>42908</t>
+          <t>41628</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>104391</t>
+          <t>109385</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>180675</t>
+          <t>182079</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -4584,12 +4584,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>46528</t>
+          <t>46386</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>81570</t>
+          <t>80262</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4599,12 +4599,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>11836</t>
+          <t>11750</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>40446</t>
+          <t>38122</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>63227</t>
+          <t>64415</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>108342</t>
+          <t>113526</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -4697,12 +4697,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>38522</t>
+          <t>37446</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>72875</t>
+          <t>70687</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>9420</t>
+          <t>9451</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>32890</t>
+          <t>33271</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>51221</t>
+          <t>52062</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>93917</t>
+          <t>97172</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>2351</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>11410</t>
+          <t>10861</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4845,12 +4845,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>9884</t>
+          <t>9721</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4880,12 +4880,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>4804</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>16443</t>
+          <t>15880</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -4923,12 +4923,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>13628</t>
+          <t>14183</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4958,12 +4958,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4973,12 +4973,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4993,12 +4993,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2557</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>14146</t>
+          <t>13438</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>12320</t>
+          <t>11597</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>28861</t>
+          <t>27407</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>15357</t>
+          <t>15415</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>34583</t>
+          <t>35146</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32D_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P32D_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>51243</t>
+          <t>53735</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41014</t>
+          <t>42347</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63976</t>
+          <t>65698</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>34157</t>
+          <t>36076</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28130</t>
+          <t>28807</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41209</t>
+          <t>43418</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>85400</t>
+          <t>89811</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73411</t>
+          <t>76332</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101752</t>
+          <t>105025</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>32,01%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>96441</t>
+          <t>101437</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83383</t>
+          <t>88295</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>110141</t>
+          <t>116817</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19002</t>
+          <t>21351</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13807</t>
+          <t>15111</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24669</t>
+          <t>28347</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>115443</t>
+          <t>122789</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101160</t>
+          <t>107555</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>131514</t>
+          <t>139260</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,44%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>50641</t>
+          <t>54212</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40347</t>
+          <t>42399</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>63818</t>
+          <t>67955</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10459</t>
+          <t>13093</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>56228</t>
+          <t>61434</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>43924</t>
+          <t>49560</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>68560</t>
+          <t>77676</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14785</t>
+          <t>16014</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8826</t>
+          <t>9868</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22725</t>
+          <t>24249</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>17055</t>
+          <t>19084</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10667</t>
+          <t>12192</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25128</t>
+          <t>29854</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8797</t>
+          <t>10471</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4299</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15133</t>
+          <t>18006</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>508</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4498</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>10522</t>
+          <t>12315</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5614</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17729</t>
+          <t>20110</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3523</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15710</t>
+          <t>15950</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1766</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>403</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>8888</t>
+          <t>9173</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>4530</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>17006</t>
+          <t>17575</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -1403,32 +1403,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3399</t>
+          <t>3419</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8182</t>
+          <t>8507</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>462</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>2578</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,32 +1473,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3854</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8574</t>
+          <t>8325</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2236</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1526,12 +1526,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>7565</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2236</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6329</t>
+          <t>8610</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -1629,32 +1629,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>5632</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11143</t>
+          <t>10376</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>8476</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1699,32 +1699,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>6814</t>
+          <t>7390</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>3383</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12582</t>
+          <t>14580</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -1742,17 +1742,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>240198</t>
+          <t>254561</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>240198</t>
+          <t>254561</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>240198</t>
+          <t>254561</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,17 +1777,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>65993</t>
+          <t>73549</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65993</t>
+          <t>73549</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65993</t>
+          <t>73549</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,17 +1812,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>306191</t>
+          <t>328111</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>306191</t>
+          <t>328111</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>306191</t>
+          <t>328111</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>208260</t>
+          <t>207555</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>173956</t>
+          <t>179170</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>246405</t>
+          <t>243291</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>409115</t>
+          <t>221614</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>277942</t>
+          <t>199888</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>575148</t>
+          <t>244440</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>617375</t>
+          <t>429169</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>454868</t>
+          <t>391272</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>998842</t>
+          <t>467925</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>404918</t>
+          <t>436060</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>367998</t>
+          <t>401106</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>438116</t>
+          <t>476609</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>172263</t>
+          <t>188670</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>167188</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>248229</t>
+          <t>208284</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>577180</t>
+          <t>624730</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>373098</t>
+          <t>582944</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>669744</t>
+          <t>667358</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>41,61%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>204601</t>
+          <t>220498</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>176755</t>
+          <t>190403</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>234585</t>
+          <t>253373</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>83643</t>
+          <t>93334</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36024</t>
+          <t>76280</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>126502</t>
+          <t>111823</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>288244</t>
+          <t>313832</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>193089</t>
+          <t>278963</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>339878</t>
+          <t>354791</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -2198,32 +2198,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>73210</t>
+          <t>75778</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54585</t>
+          <t>57771</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>94700</t>
+          <t>101425</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,32 +2233,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20742</t>
+          <t>25660</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>17596</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33898</t>
+          <t>38044</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>93952</t>
+          <t>101438</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>62025</t>
+          <t>80939</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>124156</t>
+          <t>129374</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -2311,32 +2311,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>43853</t>
+          <t>53257</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31025</t>
+          <t>37536</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>61661</t>
+          <t>73268</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2346,32 +2346,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12216</t>
+          <t>14285</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>9135</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22259</t>
+          <t>24977</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2381,32 +2381,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>56069</t>
+          <t>67542</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>34585</t>
+          <t>48597</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>75345</t>
+          <t>88260</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -2424,32 +2424,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>30924</t>
+          <t>32498</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20522</t>
+          <t>20441</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46497</t>
+          <t>49078</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2459,32 +2459,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6489</t>
+          <t>10584</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14027</t>
+          <t>20290</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2494,32 +2494,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>37413</t>
+          <t>43082</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23002</t>
+          <t>30053</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>53908</t>
+          <t>63605</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1528</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2572,32 +2572,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2318</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>735</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>7564</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2607,32 +2607,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3815</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>9828</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -2650,22 +2650,22 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>944</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10598</t>
+          <t>11400</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2720,32 +2720,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>952</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>10912</t>
+          <t>12948</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -2763,32 +2763,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>11763</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6085</t>
+          <t>7666</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19994</t>
+          <t>23302</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2798,32 +2798,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>565</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2833,32 +2833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>13689</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6896</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22493</t>
+          <t>24977</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -2876,17 +2876,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>982579</t>
+          <t>1044432</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>982579</t>
+          <t>1044432</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>982579</t>
+          <t>1044432</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2911,17 +2911,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>708712</t>
+          <t>559337</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>708712</t>
+          <t>559337</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>708712</t>
+          <t>559337</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2946,17 +2946,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1691290</t>
+          <t>1603769</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1691290</t>
+          <t>1603769</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1691290</t>
+          <t>1603769</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2993,32 +2993,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>83794</t>
+          <t>87896</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>67727</t>
+          <t>72293</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>103812</t>
+          <t>107965</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3028,32 +3028,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>102148</t>
+          <t>107049</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>89002</t>
+          <t>92587</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>115688</t>
+          <t>122301</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3063,32 +3063,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>185942</t>
+          <t>194945</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>164098</t>
+          <t>172206</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>210464</t>
+          <t>216704</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>34,18%</t>
         </is>
       </c>
     </row>
@@ -3106,32 +3106,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>135153</t>
+          <t>145986</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>114519</t>
+          <t>127037</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>152750</t>
+          <t>167647</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3141,32 +3141,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>70172</t>
+          <t>79428</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>57968</t>
+          <t>67410</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>83919</t>
+          <t>91804</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3176,32 +3176,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>205325</t>
+          <t>225414</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>181804</t>
+          <t>202185</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>230003</t>
+          <t>249762</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,39%</t>
         </is>
       </c>
     </row>
@@ -3219,32 +3219,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>69260</t>
+          <t>82200</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>54592</t>
+          <t>66062</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>87603</t>
+          <t>103691</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3254,32 +3254,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>40532</t>
+          <t>46855</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>30127</t>
+          <t>36045</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>52493</t>
+          <t>59317</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3289,32 +3289,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>109792</t>
+          <t>129055</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>91379</t>
+          <t>109924</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>131589</t>
+          <t>157106</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>24,78%</t>
         </is>
       </c>
     </row>
@@ -3332,32 +3332,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>28524</t>
+          <t>22369</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>16538</t>
+          <t>14405</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>59014</t>
+          <t>33951</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3367,32 +3367,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5951</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13815</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3402,32 +3402,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>34476</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>21658</t>
+          <t>19909</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>67896</t>
+          <t>42168</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -3445,32 +3445,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>8873</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18986</t>
+          <t>19335</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3480,32 +3480,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>11282</t>
+          <t>11838</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>21030</t>
+          <t>21172</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3515,32 +3515,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>20155</t>
+          <t>21472</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>12503</t>
+          <t>13433</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>32019</t>
+          <t>33627</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -3558,32 +3558,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>13448</t>
+          <t>14312</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7492</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22400</t>
+          <t>23025</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3593,32 +3593,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>12129</t>
+          <t>12636</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6185</t>
+          <t>6623</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>23055</t>
+          <t>24282</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3628,32 +3628,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>25577</t>
+          <t>26948</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>16368</t>
+          <t>17474</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>38089</t>
+          <t>40752</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>735</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3380</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5636</t>
+          <t>6593</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6194</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>659</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>659</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>3370</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1568</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>5457</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3932,22 +3932,22 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1582</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>423</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>4856</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3967,22 +3967,22 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7238</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -4010,17 +4010,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>342000</t>
+          <t>365370</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>342000</t>
+          <t>365370</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>342000</t>
+          <t>365370</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>244958</t>
+          <t>268627</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>244958</t>
+          <t>268627</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>244958</t>
+          <t>268627</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4080,17 +4080,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>586958</t>
+          <t>633997</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>586958</t>
+          <t>633997</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>586958</t>
+          <t>633997</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4127,32 +4127,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>343297</t>
+          <t>349186</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>301778</t>
+          <t>310140</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>385532</t>
+          <t>386226</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4162,32 +4162,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>545420</t>
+          <t>364739</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>415852</t>
+          <t>337814</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>757285</t>
+          <t>391581</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4197,32 +4197,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>888717</t>
+          <t>713925</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>729018</t>
+          <t>666631</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1309817</t>
+          <t>759465</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>29,6%</t>
         </is>
       </c>
     </row>
@@ -4240,32 +4240,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>636511</t>
+          <t>683483</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>591320</t>
+          <t>642669</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>683937</t>
+          <t>727217</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4275,32 +4275,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>261438</t>
+          <t>289450</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>145044</t>
+          <t>264945</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>335874</t>
+          <t>316358</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4310,32 +4310,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>897949</t>
+          <t>972933</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>692774</t>
+          <t>923586</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>996622</t>
+          <t>1025149</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>39,95%</t>
         </is>
       </c>
     </row>
@@ -4353,32 +4353,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>324501</t>
+          <t>356909</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>287721</t>
+          <t>320228</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>362787</t>
+          <t>396800</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4388,32 +4388,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>129762</t>
+          <t>147412</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>70917</t>
+          <t>127575</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>173051</t>
+          <t>170469</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4423,32 +4423,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>454263</t>
+          <t>504321</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>332923</t>
+          <t>460450</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>507483</t>
+          <t>546898</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -4466,32 +4466,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>116519</t>
+          <t>114161</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>94506</t>
+          <t>90839</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>151648</t>
+          <t>143297</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4501,32 +4501,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>28964</t>
+          <t>36449</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>14003</t>
+          <t>25703</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>41628</t>
+          <t>48768</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4536,32 +4536,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>145483</t>
+          <t>150610</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>109385</t>
+          <t>126634</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>182079</t>
+          <t>178733</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -4579,32 +4579,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>61524</t>
+          <t>73362</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>46386</t>
+          <t>55833</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>80262</t>
+          <t>96643</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4614,32 +4614,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>25222</t>
+          <t>27966</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>11750</t>
+          <t>18634</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>38122</t>
+          <t>38981</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4649,32 +4649,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>86746</t>
+          <t>101329</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>64415</t>
+          <t>82049</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>113526</t>
+          <t>128080</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -4692,32 +4692,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>51650</t>
+          <t>54216</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>37446</t>
+          <t>38502</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>70687</t>
+          <t>72287</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4727,32 +4727,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>20227</t>
+          <t>24986</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>9451</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>33271</t>
+          <t>38780</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4762,32 +4762,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>71877</t>
+          <t>79203</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>52062</t>
+          <t>61630</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>97172</t>
+          <t>102438</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -4805,22 +4805,22 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>5554</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2351</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>10861</t>
+          <t>10828</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4840,32 +4840,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>4875</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>9721</t>
+          <t>11313</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4875,32 +4875,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>10557</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>15880</t>
+          <t>18996</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -4918,22 +4918,22 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2601</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>14183</t>
+          <t>14892</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4988,32 +4988,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>2516</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>13438</t>
+          <t>15281</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -5031,32 +5031,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>18957</t>
+          <t>20553</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>11597</t>
+          <t>13372</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>27407</t>
+          <t>30979</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5066,32 +5066,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>5635</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>13146</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5101,32 +5101,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>23653</t>
+          <t>26187</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>15415</t>
+          <t>18292</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>35146</t>
+          <t>38322</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -5144,17 +5144,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>1564777</t>
+          <t>1664363</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1564777</t>
+          <t>1664363</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1564777</t>
+          <t>1664363</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5179,17 +5179,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>1019663</t>
+          <t>901513</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1019663</t>
+          <t>901513</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1019663</t>
+          <t>901513</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5214,17 +5214,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>2584440</t>
+          <t>2565877</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2584440</t>
+          <t>2565877</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2584440</t>
+          <t>2565877</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
